--- a/docs/excel/テスト項目書.xlsx
+++ b/docs/excel/テスト項目書.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="概要" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="結果の書き方" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="A. 画面の移動" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="B. 迷惑電話チェック（番号検索）" state="visible" r:id="rId7"/>
+    <sheet sheetId="4" name="B. 登録フォームの、迷惑番号の自動チェック" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="C. 迷惑番号一覧" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="D. 伝言の登録（登録フォーム → 確認 → 完了）" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="E. 伝言一覧・詳細" state="visible" r:id="rId10"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="344">
   <si>
     <t>伝言メモ テスト項目書（検証内容）</t>
   </si>
@@ -37,7 +37,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.1（リリース前の下書き）</t>
+    <t>0.2（リリース前の下書き。迷惑番号の確認を、登録フォームに統合）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -49,7 +49,7 @@
     <t>対象</t>
   </si>
   <si>
-    <t>コミット 8a943ce 時点の画面・API</t>
+    <t>2026-10-19 時点の画面・API</t>
   </si>
   <si>
     <t>環境</t>
@@ -115,118 +115,304 @@
     <t>/ を開く</t>
   </si>
   <si>
-    <t>/nuisance に移動し、「迷惑電話チェック」のタブが選ばれている</t>
+    <t>/register に移動し、「登録フォーム」のタブが選ばれている。電話番号の欄にカーソルがある</t>
   </si>
   <si>
     <t>画面</t>
   </si>
   <si>
+    <t>OK（10-19）</t>
+  </si>
+  <si>
+    <t>A02</t>
+  </si>
+  <si>
+    <t>タブの順番</t>
+  </si>
+  <si>
+    <t>左から「登録フォーム」「伝言一覧」「迷惑番号一覧」</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>旧 /nuisance を開く</t>
+  </si>
+  <si>
+    <t>/register に移動する（旧「迷惑電話チェック」の画面はない）</t>
+  </si>
+  <si>
+    <t>未実施（設定は、コードに入れた）</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>伝言詳細を開く</t>
+  </si>
+  <si>
+    <t>「伝言一覧」のタブが選ばれている</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>確認画面・完了画面</t>
+  </si>
+  <si>
+    <t>タブが出ない</t>
+  </si>
+  <si>
+    <t>A06</t>
+  </si>
+  <si>
+    <t>スマホ幅（390px）で、3つのタブ</t>
+  </si>
+  <si>
+    <t>同じ幅で収まり、文字が切れず、横にはみ出さない</t>
+  </si>
+  <si>
+    <t>計測</t>
+  </si>
+  <si>
+    <t>B. 登録フォームの、迷惑番号の自動チェック</t>
+  </si>
+  <si>
+    <t>B01</t>
+  </si>
+  <si>
+    <t>登録済みの番号（ハイフン付き）を入力</t>
+  </si>
+  <si>
+    <t>0.5秒後に、赤い「迷惑番号に登録されています」と、閉じたカード（電話番号と会社名）</t>
+  </si>
+  <si>
+    <t>画面（テスト環境）</t>
+  </si>
+  <si>
+    <t>B02</t>
+  </si>
+  <si>
+    <t>全角の番号を入力</t>
+  </si>
+  <si>
+    <t>B01 と同じ結果</t>
+  </si>
+  <si>
+    <t>B03</t>
+  </si>
+  <si>
+    <t>ハイフンなし、+81 付きで入力</t>
+  </si>
+  <si>
+    <t>単体（サーバー側）</t>
+  </si>
+  <si>
+    <t>OK（単体 10-14）。現在の画面は未実施</t>
+  </si>
+  <si>
+    <t>B04</t>
+  </si>
+  <si>
+    <t>未登録の番号を入力</t>
+  </si>
+  <si>
+    <t>緑の「✓ … は、迷惑番号には登録されていません」と、「迷惑番号として登録する」</t>
+  </si>
+  <si>
+    <t>B05</t>
+  </si>
+  <si>
+    <t>7桁以下の番号</t>
+  </si>
+  <si>
+    <t>結果が出ない（確認しない）</t>
+  </si>
+  <si>
+    <t>OK（10-19、4桁で確認）</t>
+  </si>
+  <si>
+    <t>B06</t>
+  </si>
+  <si>
+    <t>入力が止まる前に、続けて入力</t>
+  </si>
+  <si>
+    <t>途中の番号では確認せず、最後の番号の結果だけが出る</t>
+  </si>
+  <si>
+    <t>未実施（確認のタイミングは、0.5秒の待ちで実装）</t>
+  </si>
+  <si>
+    <t>B07</t>
+  </si>
+  <si>
+    <t>カードを開く</t>
+  </si>
+  <si>
+    <t>着信回数・最終着信・メモ・着信ログ・記録の欄が出る</t>
+  </si>
+  <si>
+    <t>OK（迷惑番号一覧のカードで 10-14）。登録フォーム内では未実施</t>
+  </si>
+  <si>
+    <t>B08</t>
+  </si>
+  <si>
+    <t>「今回の着信を記録する」</t>
+  </si>
+  <si>
+    <t>回数が増え、「記録しました（通算N回目）」と出る</t>
+  </si>
+  <si>
+    <t>API／画面</t>
+  </si>
+  <si>
+    <t>API OK（10-14）。画面は未実施</t>
+  </si>
+  <si>
+    <t>B09</t>
+  </si>
+  <si>
+    <t>「迷惑番号として登録する」</t>
+  </si>
+  <si>
+    <t>迷惑番号一覧の登録フォームが開き、番号が入っている</t>
+  </si>
+  <si>
+    <t>B10</t>
+  </si>
+  <si>
+    <t>電話番号を入れて「確認」へ</t>
+  </si>
+  <si>
+    <t>本文の最後に「TEL：番号」が1行入る</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>確認画面の「修正する」→ もう一度「確認」</t>
+  </si>
+  <si>
+    <t>電話番号が残る。「TEL：」の行が重ならない</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>電話番号を入れずに登録</t>
+  </si>
+  <si>
+    <t>従来どおり、登録できる</t>
+  </si>
+  <si>
+    <t>B13</t>
+  </si>
+  <si>
+    <t>確認の通信に失敗</t>
+  </si>
+  <si>
+    <t>エラーの文言が出る。登録フォームは使える</t>
+  </si>
+  <si>
+    <t>C. 迷惑番号一覧</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>一覧を開く</t>
+  </si>
+  <si>
+    <t>各カードは、電話番号と会社名だけの2行の帯</t>
+  </si>
+  <si>
+    <t>画面（仮データ）</t>
+  </si>
+  <si>
     <t>OK（10-14）</t>
   </si>
   <si>
-    <t>A02</t>
-  </si>
-  <si>
-    <t>タブの順番</t>
-  </si>
-  <si>
-    <t>左から「迷惑電話チェック」「登録フォーム」「伝言一覧」</t>
-  </si>
-  <si>
-    <t>A03</t>
-  </si>
-  <si>
-    <t>各タブをクリック</t>
-  </si>
-  <si>
-    <t>それぞれ /nuisance、/register、/list に移動する</t>
-  </si>
-  <si>
-    <t>A04</t>
-  </si>
-  <si>
-    <t>伝言詳細を開く</t>
-  </si>
-  <si>
-    <t>「伝言一覧」のタブが選ばれている</t>
-  </si>
-  <si>
-    <t>A05</t>
-  </si>
-  <si>
-    <t>確認画面・完了画面</t>
-  </si>
-  <si>
-    <t>タブが出ない</t>
-  </si>
-  <si>
-    <t>A06</t>
-  </si>
-  <si>
-    <t>スマホ幅（390px）で、3つのタブ</t>
-  </si>
-  <si>
-    <t>同じ幅で収まり、文字が切れず、横にはみ出さない</t>
-  </si>
-  <si>
-    <t>計測</t>
-  </si>
-  <si>
-    <t>B. 迷惑電話チェック（番号検索）</t>
-  </si>
-  <si>
-    <t>B01</t>
-  </si>
-  <si>
-    <t>登録済みの番号（ハイフン付き）を検索</t>
-  </si>
-  <si>
-    <t>赤い「迷惑番号に登録されています」と、開いたカード</t>
-  </si>
-  <si>
-    <t>画面（テスト環境）</t>
-  </si>
-  <si>
-    <t>B02</t>
-  </si>
-  <si>
-    <t>全角の番号を検索</t>
-  </si>
-  <si>
-    <t>B01 と同じ結果</t>
-  </si>
-  <si>
-    <t>B03</t>
-  </si>
-  <si>
-    <t>ハイフンなし、+81 付きで検索</t>
-  </si>
-  <si>
-    <t>単体（サーバー側）／旧画面</t>
-  </si>
-  <si>
-    <t>OK（単体 10-14、旧画面 10-08）。現在の画面は未実施</t>
-  </si>
-  <si>
-    <t>B04</t>
-  </si>
-  <si>
-    <t>未登録の番号を検索</t>
-  </si>
-  <si>
-    <t>緑の「登録なし」と、2つのボタン</t>
-  </si>
-  <si>
-    <t>画面（仮データ）</t>
-  </si>
-  <si>
-    <t>B05</t>
-  </si>
-  <si>
-    <t>空欄、7桁以下で検索</t>
-  </si>
-  <si>
-    <t>エラーの文言。検索されない</t>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>カードをクリック</t>
+  </si>
+  <si>
+    <t>開いて、着信回数・最終着信・メモ・着信ログ・記録の欄・編集・削除が出る。もう一度で閉じる</t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>テスト環境で一覧を開く</t>
+  </si>
+  <si>
+    <t>AWS（NuisanceNumbers-test）の5件が出る</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t>全角の番号で新規登録</t>
+  </si>
+  <si>
+    <t>登録でき、一覧に出る（番号は整えられる）</t>
+  </si>
+  <si>
+    <t>C05</t>
+  </si>
+  <si>
+    <t>同じ番号を再登録</t>
+  </si>
+  <si>
+    <t>「この番号はすでに登録されています」</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>OK（409、10-14）。画面は未実施</t>
+  </si>
+  <si>
+    <t>C06</t>
+  </si>
+  <si>
+    <t>桁数が足りない番号を登録</t>
+  </si>
+  <si>
+    <t>「電話番号の桁数を確認してください」</t>
+  </si>
+  <si>
+    <t>OK（400、10-14）。画面は未実施</t>
+  </si>
+  <si>
+    <t>C07</t>
+  </si>
+  <si>
+    <t>編集（会社名・メモ）</t>
+  </si>
+  <si>
+    <t>保存される。番号は変えられない</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>削除（確認ダイアログ→OK）</t>
+  </si>
+  <si>
+    <t>一覧から消え、AWS 側でも消える</t>
+  </si>
+  <si>
+    <t>C09</t>
+  </si>
+  <si>
+    <t>削除（確認ダイアログ→キャンセル）</t>
+  </si>
+  <si>
+    <t>消えない</t>
   </si>
   <si>
     <t>旧画面</t>
@@ -235,141 +421,6 @@
     <t>OK（10-08）。現在の画面は未実施</t>
   </si>
   <si>
-    <t>B06</t>
-  </si>
-  <si>
-    <t>「伝言を登録する」</t>
-  </si>
-  <si>
-    <t>/register が開き、本文に TEL：番号 が入っている</t>
-  </si>
-  <si>
-    <t>B07</t>
-  </si>
-  <si>
-    <t>「迷惑番号として登録する」</t>
-  </si>
-  <si>
-    <t>迷惑番号一覧の登録フォームが開き、番号が入っている</t>
-  </si>
-  <si>
-    <t>B08</t>
-  </si>
-  <si>
-    <t>「今回の着信を記録する」</t>
-  </si>
-  <si>
-    <t>回数が増え、「記録しました（通算N回目）」と出る</t>
-  </si>
-  <si>
-    <t>API／画面</t>
-  </si>
-  <si>
-    <t>API OK（10-14）。画面は未実施</t>
-  </si>
-  <si>
-    <t>B09</t>
-  </si>
-  <si>
-    <t>検索の通信に失敗</t>
-  </si>
-  <si>
-    <t>エラーの文言が出る。画面は壊れない</t>
-  </si>
-  <si>
-    <t>C. 迷惑番号一覧</t>
-  </si>
-  <si>
-    <t>C01</t>
-  </si>
-  <si>
-    <t>一覧を開く</t>
-  </si>
-  <si>
-    <t>各カードは、電話番号と会社名だけの2行の帯</t>
-  </si>
-  <si>
-    <t>C02</t>
-  </si>
-  <si>
-    <t>カードをクリック</t>
-  </si>
-  <si>
-    <t>開いて、着信回数・最終着信・メモ・着信ログ・記録の欄・編集・削除が出る。もう一度で閉じる</t>
-  </si>
-  <si>
-    <t>C03</t>
-  </si>
-  <si>
-    <t>テスト環境で一覧を開く</t>
-  </si>
-  <si>
-    <t>AWS（NuisanceNumbers-test）の5件が出る</t>
-  </si>
-  <si>
-    <t>C04</t>
-  </si>
-  <si>
-    <t>全角の番号で新規登録</t>
-  </si>
-  <si>
-    <t>登録でき、一覧に出る（番号は整えられる）</t>
-  </si>
-  <si>
-    <t>C05</t>
-  </si>
-  <si>
-    <t>同じ番号を再登録</t>
-  </si>
-  <si>
-    <t>「この番号はすでに登録されています」</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>OK（409、10-14）。画面は未実施</t>
-  </si>
-  <si>
-    <t>C06</t>
-  </si>
-  <si>
-    <t>桁数が足りない番号を登録</t>
-  </si>
-  <si>
-    <t>「電話番号の桁数を確認してください」</t>
-  </si>
-  <si>
-    <t>OK（400、10-14）。画面は未実施</t>
-  </si>
-  <si>
-    <t>C07</t>
-  </si>
-  <si>
-    <t>編集（会社名・メモ）</t>
-  </si>
-  <si>
-    <t>保存される。番号は変えられない</t>
-  </si>
-  <si>
-    <t>C08</t>
-  </si>
-  <si>
-    <t>削除（確認ダイアログ→OK）</t>
-  </si>
-  <si>
-    <t>一覧から消え、AWS 側でも消える</t>
-  </si>
-  <si>
-    <t>C09</t>
-  </si>
-  <si>
-    <t>削除（確認ダイアログ→キャンセル）</t>
-  </si>
-  <si>
-    <t>消えない</t>
-  </si>
-  <si>
     <t>C10</t>
   </si>
   <si>
@@ -874,7 +925,7 @@
     <t>出ない</t>
   </si>
   <si>
-    <t>登録フォーム・伝言一覧は OK（10-14）。迷惑電話チェック・迷惑番号一覧は、現在のデザインでは未実施</t>
+    <t>登録フォーム・伝言一覧は OK（10-14）。迷惑番号一覧は、現在のデザインでは未実施</t>
   </si>
   <si>
     <t>I06</t>
@@ -985,7 +1036,7 @@
     <t>P01</t>
   </si>
   <si>
-    <t>画面が開き、最初の画面が「迷惑電話チェック」になる</t>
+    <t>画面が開き、最初の画面が「登録フォーム」になる。電話番号の欄にカーソルがある</t>
   </si>
   <si>
     <t>P02</t>
@@ -1500,7 +1551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1565,7 +1616,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1591,47 +1642,47 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
@@ -1642,53 +1693,53 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -1716,7 +1767,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1742,33 +1793,33 @@
     </row>
     <row r="4" ht="52" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>20</v>
@@ -1776,13 +1827,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
@@ -1793,16 +1844,16 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>20</v>
@@ -1810,36 +1861,36 @@
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1866,7 +1917,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1880,7 +1931,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -1888,114 +1939,114 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -2021,14 +2072,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -2044,12 +2095,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>20</v>
@@ -2057,10 +2108,10 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>20</v>
@@ -2068,10 +2119,10 @@
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>20</v>
@@ -2079,10 +2130,10 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>20</v>
@@ -2185,7 +2236,7 @@
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="8" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2261,19 +2312,19 @@
       <c r="D6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>32</v>
+      <c r="E6" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>31</v>
@@ -2284,13 +2335,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>31</v>
@@ -2301,16 +2352,16 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>32</v>
@@ -2329,19 +2380,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="3" width="52" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="52" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2365,18 +2416,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>32</v>
@@ -2384,16 +2435,16 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>53</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -2401,33 +2452,33 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>32</v>
@@ -2444,30 +2495,30 @@
         <v>67</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>68</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>73</v>
       </c>
@@ -2478,43 +2529,111 @@
         <v>75</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>20</v>
+        <v>54</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E15" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2543,7 +2662,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2569,166 +2688,166 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>69</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>31</v>
@@ -2739,13 +2858,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>31</v>
@@ -2756,19 +2875,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2796,7 +2915,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2822,13 +2941,13 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>31</v>
@@ -2839,67 +2958,67 @@
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>20</v>
@@ -2907,53 +3026,53 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2981,7 +3100,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3007,115 +3126,115 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>174</v>
+        <v>191</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>31</v>
@@ -3126,13 +3245,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>31</v>
@@ -3166,7 +3285,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3175,7 +3294,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>178</v>
+        <v>195</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -3201,138 +3320,138 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -3360,7 +3479,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3368,7 +3487,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -3390,13 +3509,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>16</v>
@@ -3404,13 +3523,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>16</v>
@@ -3418,13 +3537,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>16</v>
@@ -3432,13 +3551,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>16</v>
@@ -3446,13 +3565,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>16</v>
@@ -3460,13 +3579,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>16</v>
@@ -3474,13 +3593,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>16</v>
@@ -3488,13 +3607,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>16</v>
@@ -3502,13 +3621,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>16</v>
@@ -3516,13 +3635,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>16</v>
@@ -3530,13 +3649,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>16</v>
@@ -3544,13 +3663,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>20</v>
@@ -3558,13 +3677,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>16</v>

--- a/docs/excel/テスト項目書.xlsx
+++ b/docs/excel/テスト項目書.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="374">
   <si>
     <t>伝言メモ テスト項目書（検証内容）</t>
   </si>
@@ -37,7 +37,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.2（リリース前の下書き。迷惑番号の確認を、登録フォームに統合）</t>
+    <t>0.3（リリース前の下書き。登録フォームから、直接の登録もできる）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -316,6 +316,99 @@
     <t>エラーの文言が出る。登録フォームは使える</t>
   </si>
   <si>
+    <t>B14</t>
+  </si>
+  <si>
+    <t>未登録の番号が出たとき</t>
+  </si>
+  <si>
+    <t>「このまま伝言を登録する」と「迷惑番号として登録する」の2つのボタンが出る</t>
+  </si>
+  <si>
+    <t>B15</t>
+  </si>
+  <si>
+    <t>必須が空のまま「このまま伝言を登録する」</t>
+  </si>
+  <si>
+    <t>ボタンの下に「伝言内容を入力してください」など。登録されず、画面も移らない</t>
+  </si>
+  <si>
+    <t>OK（10-19、伝言内容が空の場合のみ。自分の名前・伝言先が空の場合は未実施）</t>
+  </si>
+  <si>
+    <t>B16</t>
+  </si>
+  <si>
+    <t>必須を入れて「このまま伝言を登録する」</t>
+  </si>
+  <si>
+    <t>確認画面を通らず、伝言一覧に移る。上に「〇〇 宛の伝言を登録しました。」と通知の文言。登録した伝言が、いちばん上。本文の最後に「TEL：番号」</t>
+  </si>
+  <si>
+    <t>B17</t>
+  </si>
+  <si>
+    <t>B16 の、Teams「99_テスト」への通知</t>
+  </si>
+  <si>
+    <t>届く。本番「71_伝言メモ」には届かない</t>
+  </si>
+  <si>
+    <t>目視</t>
+  </si>
+  <si>
+    <t>未実施（10-19 に、通知の送信は発生。人の目視は未実施）</t>
+  </si>
+  <si>
+    <t>B18</t>
+  </si>
+  <si>
+    <t>B16 で、登録に失敗（API の応答が SUCCESS 以外）</t>
+  </si>
+  <si>
+    <t>「伝言を登録できませんでした。もう一度お試しください」。入力は残る</t>
+  </si>
+  <si>
+    <t>B19</t>
+  </si>
+  <si>
+    <t>「迷惑番号として登録する」→ 会社名・メモ →「登録する」</t>
+  </si>
+  <si>
+    <t>画面を移らず、迷惑番号に登録される（着信ログ1件、対応者は自分の名前）。赤い札とカードが出る</t>
+  </si>
+  <si>
+    <t>B20</t>
+  </si>
+  <si>
+    <t>B19 で、同じ番号がすでにあるとき（確認のあとに、ほかの人が登録した場合など）</t>
+  </si>
+  <si>
+    <t>「この番号はすでに登録されています」。フォームは開いたまま</t>
+  </si>
+  <si>
+    <t>未実施（API は 409：G05）</t>
+  </si>
+  <si>
+    <t>B21</t>
+  </si>
+  <si>
+    <t>B19 の「やめる」</t>
+  </si>
+  <si>
+    <t>フォームが閉じる。登録されない</t>
+  </si>
+  <si>
+    <t>B22</t>
+  </si>
+  <si>
+    <t>仮データ（npm run dev、設定なし）で B16</t>
+  </si>
+  <si>
+    <t>伝言一覧に移り、「テストモードのため、Teamsには通知していません。」</t>
+  </si>
+  <si>
     <t>C. 迷惑番号一覧</t>
   </si>
   <si>
@@ -493,7 +586,7 @@
     <t>D05</t>
   </si>
   <si>
-    <t>テスト環境で「最終OK」</t>
+    <t>テスト環境で「最終OK」（確認を通る登録）</t>
   </si>
   <si>
     <t>「テスト用チャネル（99_テスト）へ通知しました。」。本番へのリンクは出ない</t>
@@ -508,9 +601,6 @@
     <t>届く。差出人が mako.iwata@gravityoffice365.onmicrosoft.com（アイコンあり）</t>
   </si>
   <si>
-    <t>目視</t>
-  </si>
-  <si>
     <t>OK（10-09、岩田）</t>
   </si>
   <si>
@@ -1048,7 +1138,7 @@
     <t>P03</t>
   </si>
   <si>
-    <t>本番で伝言を1件登録 → 「71_伝言メモ」に届く → 一覧に出る → 削除</t>
+    <t>本番で伝言を1件登録（確認を通る登録と、「このまま伝言を登録する」の両方）→ 「71_伝言メモ」に届く → 一覧に出る → 削除</t>
   </si>
   <si>
     <t>P04</t>
@@ -1616,7 +1706,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1642,47 +1732,47 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
@@ -1693,53 +1783,53 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>275</v>
+        <v>305</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>282</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -1767,7 +1857,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1793,33 +1883,33 @@
     </row>
     <row r="4" ht="52" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>284</v>
+        <v>314</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>285</v>
+        <v>315</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>286</v>
+        <v>316</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>287</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>288</v>
+        <v>318</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>289</v>
+        <v>319</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>290</v>
+        <v>320</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>20</v>
@@ -1827,13 +1917,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>293</v>
+        <v>323</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
@@ -1844,13 +1934,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>294</v>
+        <v>324</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>295</v>
+        <v>325</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>49</v>
@@ -1861,36 +1951,36 @@
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>299</v>
+        <v>329</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>301</v>
+        <v>331</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>302</v>
+        <v>332</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1917,7 +2007,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>304</v>
+        <v>334</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1931,7 +2021,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -1939,114 +2029,114 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>316</v>
+        <v>346</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>317</v>
+        <v>347</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>321</v>
+        <v>351</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>322</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>323</v>
+        <v>353</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>325</v>
+        <v>355</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>326</v>
+        <v>356</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>327</v>
+        <v>357</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>328</v>
+        <v>358</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>329</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -2072,14 +2162,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>334</v>
+        <v>364</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>335</v>
+        <v>365</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -2097,10 +2187,10 @@
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>20</v>
@@ -2108,21 +2198,21 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" ht="52" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>20</v>
@@ -2130,10 +2220,10 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>343</v>
+        <v>373</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>20</v>
@@ -2380,12 +2470,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="43" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="2" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
@@ -2634,6 +2723,159 @@
         <v>31</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2662,7 +2904,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2688,118 +2930,118 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>118</v>
+        <v>149</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>120</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>81</v>
@@ -2807,47 +3049,47 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>31</v>
@@ -2858,13 +3100,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>31</v>
@@ -2875,19 +3117,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>141</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2915,7 +3157,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2941,13 +3183,13 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>145</v>
+        <v>176</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>31</v>
@@ -2958,64 +3200,64 @@
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>54</v>
@@ -3026,53 +3268,53 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>161</v>
+        <v>110</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -3100,7 +3342,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3126,115 +3368,115 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>80</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>187</v>
+        <v>217</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>191</v>
+        <v>221</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>31</v>
@@ -3245,13 +3487,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>31</v>
@@ -3285,7 +3527,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3294,7 +3536,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -3320,138 +3562,138 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>204</v>
+        <v>234</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>206</v>
+        <v>236</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>208</v>
+        <v>238</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>212</v>
+        <v>242</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>214</v>
+        <v>244</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>217</v>
+        <v>247</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -3479,7 +3721,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3487,7 +3729,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -3509,13 +3751,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>225</v>
+        <v>255</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>16</v>
@@ -3523,13 +3765,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>16</v>
@@ -3537,13 +3779,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>229</v>
+        <v>259</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>231</v>
+        <v>261</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>16</v>
@@ -3551,13 +3793,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>232</v>
+        <v>262</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>234</v>
+        <v>264</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>16</v>
@@ -3565,13 +3807,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>236</v>
+        <v>266</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>16</v>
@@ -3579,13 +3821,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>238</v>
+        <v>268</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>16</v>
@@ -3593,13 +3835,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>16</v>
@@ -3607,13 +3849,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>16</v>
@@ -3621,13 +3863,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>16</v>
@@ -3635,13 +3877,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>16</v>
@@ -3649,13 +3891,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>16</v>
@@ -3663,13 +3905,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>20</v>
@@ -3677,13 +3919,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>16</v>

--- a/docs/excel/テスト項目書.xlsx
+++ b/docs/excel/テスト項目書.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="392">
   <si>
     <t>伝言メモ テスト項目書（検証内容）</t>
   </si>
@@ -37,7 +37,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.3（リリース前の下書き。登録フォームから、直接の登録もできる）</t>
+    <t>0.4（リリース前の下書き。ボタンの色の使い分けを追加）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -1025,6 +1025,60 @@
   </si>
   <si>
     <t>ja、「伝言メモ」、メモ帳とえんぴつ</t>
+  </si>
+  <si>
+    <t>I07</t>
+  </si>
+  <si>
+    <t>ボタンの色の使い分け</t>
+  </si>
+  <si>
+    <t>伝言の登録＝緑、迷惑番号の登録・着信の記録・新規登録＝黄、削除＝赤、副次的な操作＝白地に緑の枠</t>
+  </si>
+  <si>
+    <t>OK（10-20、登録フォームと迷惑番号一覧で、ボタンの色を取得して確認）</t>
+  </si>
+  <si>
+    <t>I08</t>
+  </si>
+  <si>
+    <t>黄のボタンのコントラスト</t>
+  </si>
+  <si>
+    <t>文字と背景が 4.5:1 以上</t>
+  </si>
+  <si>
+    <t>OK（10-20。濃い茶色の文字／黄の背景で 8.2:1、ホバー時 7.0:1）</t>
+  </si>
+  <si>
+    <t>I09</t>
+  </si>
+  <si>
+    <t>幅の狭い画面（390px）で、登録なしの2つのボタン</t>
+  </si>
+  <si>
+    <t>縦に並び、幅いっぱいで、高さ44px</t>
+  </si>
+  <si>
+    <t>OK（10-20）</t>
+  </si>
+  <si>
+    <t>I10</t>
+  </si>
+  <si>
+    <t>通信中のボタン</t>
+  </si>
+  <si>
+    <t>押せず、くるくる回る印が出る</t>
+  </si>
+  <si>
+    <t>I11</t>
+  </si>
+  <si>
+    <t>登録直後のお知らせの「×」</t>
+  </si>
+  <si>
+    <t>お知らせが閉じる</t>
   </si>
   <si>
     <t>J. ビルド・静的チェック</t>
@@ -1641,7 +1695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1845,13 +1899,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1981,6 +2035,91 @@
       </c>
       <c r="E9" s="10" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2007,7 +2146,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2021,7 +2160,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -2029,13 +2168,13 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>133</v>
@@ -2043,27 +2182,27 @@
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>133</v>
@@ -2071,13 +2210,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>133</v>
@@ -2085,27 +2224,27 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>133</v>
@@ -2113,30 +2252,30 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -2162,14 +2301,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -2187,10 +2326,10 @@
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>20</v>
@@ -2198,10 +2337,10 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>20</v>
@@ -2209,10 +2348,10 @@
     </row>
     <row r="8" ht="52" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>20</v>
@@ -2220,10 +2359,10 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>20</v>

--- a/docs/excel/テスト項目書.xlsx
+++ b/docs/excel/テスト項目書.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="402">
   <si>
     <t>伝言メモ テスト項目書（検証内容）</t>
   </si>
@@ -37,7 +37,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.4（リリース前の下書き。ボタンの色の使い分けを追加）</t>
+    <t>0.5（リリース前の下書き。緑のボタンを1つにまとめた）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -322,30 +322,36 @@
     <t>未登録の番号が出たとき</t>
   </si>
   <si>
-    <t>「このまま伝言を登録する」と「迷惑番号として登録する」の2つのボタンが出る</t>
+    <t>黄の「迷惑番号として登録する」だけが出る（緑のボタンは、フォーム下の「登録する」の1つだけ）</t>
+  </si>
+  <si>
+    <t>OK（10-20）</t>
   </si>
   <si>
     <t>B15</t>
   </si>
   <si>
-    <t>必須が空のまま「このまま伝言を登録する」</t>
-  </si>
-  <si>
-    <t>ボタンの下に「伝言内容を入力してください」など。登録されず、画面も移らない</t>
-  </si>
-  <si>
-    <t>OK（10-19、伝言内容が空の場合のみ。自分の名前・伝言先が空の場合は未実施）</t>
+    <t>必須が空のまま、フォーム下の「登録する」</t>
+  </si>
+  <si>
+    <t>ボタンの上に「伝言内容を入力してください」など。登録されず、画面も移らない</t>
+  </si>
+  <si>
+    <t>OK（10-20、伝言内容が空の場合のみ。自分の名前・伝言先が空の場合は未実施）</t>
   </si>
   <si>
     <t>B16</t>
   </si>
   <si>
-    <t>必須を入れて「このまま伝言を登録する」</t>
+    <t>必須を入れて、フォーム下の「登録する」</t>
   </si>
   <si>
     <t>確認画面を通らず、伝言一覧に移る。上に「〇〇 宛の伝言を登録しました。」と通知の文言。登録した伝言が、いちばん上。本文の最後に「TEL：番号」</t>
   </si>
   <si>
+    <t>OK（10-19。ボタンの位置の変更後は、押す操作が未実施）</t>
+  </si>
+  <si>
     <t>B17</t>
   </si>
   <si>
@@ -1060,9 +1066,6 @@
     <t>縦に並び、幅いっぱいで、高さ44px</t>
   </si>
   <si>
-    <t>OK（10-20）</t>
-  </si>
-  <si>
     <t>I10</t>
   </si>
   <si>
@@ -1081,6 +1084,33 @@
     <t>お知らせが閉じる</t>
   </si>
   <si>
+    <t>I12</t>
+  </si>
+  <si>
+    <t>緑の主な操作の数（登録フォーム）</t>
+  </si>
+  <si>
+    <t>緑のボタンは、フォーム下の「登録する」の1つだけ（電話番号の確認の結果が出ても、増えない）</t>
+  </si>
+  <si>
+    <t>I13</t>
+  </si>
+  <si>
+    <t>「確認してから登録する」</t>
+  </si>
+  <si>
+    <t>確認画面に進む（本文に「TEL：」の行）</t>
+  </si>
+  <si>
+    <t>I14</t>
+  </si>
+  <si>
+    <t>幅の狭い画面（390px）の、フォーム下の2つのボタン</t>
+  </si>
+  <si>
+    <t>縦に並び（緑が上）、幅いっぱい、高さ52px、横にはみ出さない</t>
+  </si>
+  <si>
     <t>J. ビルド・静的チェック</t>
   </si>
   <si>
@@ -1192,7 +1222,7 @@
     <t>P03</t>
   </si>
   <si>
-    <t>本番で伝言を1件登録（確認を通る登録と、「このまま伝言を登録する」の両方）→ 「71_伝言メモ」に届く → 一覧に出る → 削除</t>
+    <t>本番で伝言を1件登録（「登録する」と、「確認してから登録する」の両方）→ 「71_伝言メモ」に届く → 一覧に出る → 削除</t>
   </si>
   <si>
     <t>P04</t>
@@ -1760,7 +1790,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1786,47 +1816,47 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
@@ -1837,53 +1867,53 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -1899,7 +1929,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1911,7 +1941,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1937,33 +1967,33 @@
     </row>
     <row r="4" ht="52" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>20</v>
@@ -1971,13 +2001,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
@@ -1988,13 +2018,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>49</v>
@@ -2005,98 +2035,98 @@
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>345</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>31</v>
@@ -2107,19 +2137,70 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2146,7 +2227,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2160,7 +2241,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -2168,114 +2249,114 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
     </row>
   </sheetData>
@@ -2301,14 +2382,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -2326,10 +2407,10 @@
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>20</v>
@@ -2337,21 +2418,21 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="52" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>20</v>
@@ -2359,10 +2440,10 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>20</v>
@@ -2879,69 +2960,69 @@
         <v>54</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" ht="52" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>31</v>
@@ -2952,13 +3033,13 @@
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>54</v>
@@ -2969,30 +3050,30 @@
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>31</v>
@@ -3003,13 +3084,13 @@
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>31</v>
@@ -3043,7 +3124,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3069,118 +3150,118 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="E5" s="10" t="s">
         <v>135</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>146</v>
-      </c>
       <c r="E9" s="10" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>81</v>
@@ -3188,47 +3269,47 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>31</v>
@@ -3239,13 +3320,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>31</v>
@@ -3256,19 +3337,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -3296,7 +3377,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3322,13 +3403,13 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>31</v>
@@ -3339,64 +3420,64 @@
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>54</v>
@@ -3407,53 +3488,53 @@
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -3481,7 +3562,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3507,115 +3588,115 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>80</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>31</v>
@@ -3626,13 +3707,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>31</v>
@@ -3666,7 +3747,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3675,7 +3756,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -3701,138 +3782,138 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -3860,7 +3941,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3868,7 +3949,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -3890,13 +3971,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>16</v>
@@ -3904,13 +3985,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>16</v>
@@ -3918,13 +3999,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>16</v>
@@ -3932,13 +4013,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>16</v>
@@ -3946,13 +4027,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>16</v>
@@ -3960,13 +4041,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>16</v>
@@ -3974,13 +4055,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>16</v>
@@ -3988,13 +4069,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>16</v>
@@ -4002,13 +4083,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>16</v>
@@ -4016,13 +4097,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>279</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>16</v>
@@ -4030,13 +4111,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>16</v>
@@ -4044,13 +4125,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>20</v>
@@ -4058,13 +4139,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>16</v>

--- a/docs/excel/テスト項目書.xlsx
+++ b/docs/excel/テスト項目書.xlsx
@@ -9,7 +9,7 @@
     <sheet sheetId="3" name="A. 画面の移動" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="B. 登録フォームの、迷惑番号の自動チェック" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="C. 迷惑番号一覧" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="D. 伝言の登録（登録フォーム → 確認 → 完了）" state="visible" r:id="rId9"/>
+    <sheet sheetId="6" name="D. 伝言の登録（登録フォーム → 伝言一覧）" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="E. 伝言一覧・詳細" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="F. API（伝言）" state="visible" r:id="rId11"/>
     <sheet sheetId="9" name="G. API（迷惑番号）" state="visible" r:id="rId12"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="382">
   <si>
     <t>伝言メモ テスト項目書（検証内容）</t>
   </si>
@@ -37,7 +37,7 @@
     <t>版</t>
   </si>
   <si>
-    <t>0.5（リリース前の下書き。緑のボタンを1つにまとめた）</t>
+    <t>0.6（リリース前の下書き。確認画面・完了画面をなくし、枠のデザインを整理）</t>
   </si>
   <si>
     <t>作成日</t>
@@ -154,15 +154,6 @@
     <t>「伝言一覧」のタブが選ばれている</t>
   </si>
   <si>
-    <t>A05</t>
-  </si>
-  <si>
-    <t>確認画面・完了画面</t>
-  </si>
-  <si>
-    <t>タブが出ない</t>
-  </si>
-  <si>
     <t>A06</t>
   </si>
   <si>
@@ -280,24 +271,6 @@
     <t>迷惑番号一覧の登録フォームが開き、番号が入っている</t>
   </si>
   <si>
-    <t>B10</t>
-  </si>
-  <si>
-    <t>電話番号を入れて「確認」へ</t>
-  </si>
-  <si>
-    <t>本文の最後に「TEL：番号」が1行入る</t>
-  </si>
-  <si>
-    <t>B11</t>
-  </si>
-  <si>
-    <t>確認画面の「修正する」→ もう一度「確認」</t>
-  </si>
-  <si>
-    <t>電話番号が残る。「TEL：」の行が重ならない</t>
-  </si>
-  <si>
     <t>B12</t>
   </si>
   <si>
@@ -550,7 +523,7 @@
     <t>OK（10-14、テスト用 API に迷惑番号のルートがなかったとき、担当者が確認）</t>
   </si>
   <si>
-    <t>D. 伝言の登録（登録フォーム → 確認 → 完了）</t>
+    <t>D. 伝言の登録（登録フォーム → 伝言一覧）</t>
   </si>
   <si>
     <t>D01</t>
@@ -565,37 +538,10 @@
     <t>D02</t>
   </si>
   <si>
-    <t>電話先ありで「確認」へ</t>
-  </si>
-  <si>
-    <t>確認画面に、電話先・伝言内容・受電者・伝言先が分かれて出る。改行が残る。【電話先】の表記は出ない</t>
-  </si>
-  <si>
-    <t>D03</t>
-  </si>
-  <si>
-    <t>確認画面の「修正する」</t>
-  </si>
-  <si>
-    <t>登録フォームに戻り、入力内容が残っている</t>
-  </si>
-  <si>
-    <t>D04</t>
-  </si>
-  <si>
-    <t>「最終OK」</t>
-  </si>
-  <si>
-    <t>完了画面。仮データのときは「テストモードのため、Teamsには通知していません。」</t>
-  </si>
-  <si>
-    <t>D05</t>
-  </si>
-  <si>
-    <t>テスト環境で「最終OK」（確認を通る登録）</t>
-  </si>
-  <si>
-    <t>「テスト用チャネル（99_テスト）へ通知しました。」。本番へのリンクは出ない</t>
+    <t>「登録する」（確認画面なし）</t>
+  </si>
+  <si>
+    <t>伝言一覧に移り、登録した伝言が、いちばん上に出る（B16 と同じ）</t>
   </si>
   <si>
     <t>D06</t>
@@ -619,15 +565,6 @@
     <t>テストの通知が届いていない</t>
   </si>
   <si>
-    <t>D08</t>
-  </si>
-  <si>
-    <t>完了画面の「新しい伝言を登録する」</t>
-  </si>
-  <si>
-    <t>/register が開く</t>
-  </si>
-  <si>
     <t>E. 伝言一覧・詳細</t>
   </si>
   <si>
@@ -1084,31 +1021,34 @@
     <t>お知らせが閉じる</t>
   </si>
   <si>
+    <t>I15</t>
+  </si>
+  <si>
+    <t>枠のデザイン（伝言一覧・迷惑番号一覧・詳細）</t>
+  </si>
+  <si>
+    <t>薄い緑の縞の枠に、白い面。上にテープ風の印。濃い緑の帯・点線・チェック柄がない</t>
+  </si>
+  <si>
+    <t>OK（10-20、伝言一覧・迷惑番号一覧。詳細・登録フォームの確認の枠は、未実施）</t>
+  </si>
+  <si>
     <t>I12</t>
   </si>
   <si>
     <t>緑の主な操作の数（登録フォーム）</t>
   </si>
   <si>
-    <t>緑のボタンは、フォーム下の「登録する」の1つだけ（電話番号の確認の結果が出ても、増えない）</t>
-  </si>
-  <si>
-    <t>I13</t>
-  </si>
-  <si>
-    <t>「確認してから登録する」</t>
-  </si>
-  <si>
-    <t>確認画面に進む（本文に「TEL：」の行）</t>
+    <t>緑のボタンは、フォーム下の「登録する」の1つだけ（電話番号の確認の結果が出ても、増えない）。ボタンは真ん中</t>
   </si>
   <si>
     <t>I14</t>
   </si>
   <si>
-    <t>幅の狭い画面（390px）の、フォーム下の2つのボタン</t>
-  </si>
-  <si>
-    <t>縦に並び（緑が上）、幅いっぱい、高さ52px、横にはみ出さない</t>
+    <t>幅の狭い画面（390px）の、フォーム下の「登録する」</t>
+  </si>
+  <si>
+    <t>幅いっぱい、真ん中、高さ52px、横にはみ出さない</t>
   </si>
   <si>
     <t>J. ビルド・静的チェック</t>
@@ -1222,7 +1162,7 @@
     <t>P03</t>
   </si>
   <si>
-    <t>本番で伝言を1件登録（「登録する」と、「確認してから登録する」の両方）→ 「71_伝言メモ」に届く → 一覧に出る → 削除</t>
+    <t>本番で伝言を1件登録（フォーム下の「登録する」）→ 「71_伝言メモ」に届く → 一覧に出る → 削除</t>
   </si>
   <si>
     <t>P04</t>
@@ -1725,7 +1665,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" ht="36" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1790,7 +1730,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1816,47 +1756,47 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
@@ -1867,53 +1807,53 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -1941,7 +1881,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1967,33 +1907,33 @@
     </row>
     <row r="4" ht="52" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>20</v>
@@ -2001,13 +1941,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>31</v>
@@ -2018,16 +1958,16 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>20</v>
@@ -2035,98 +1975,98 @@
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>332</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>31</v>
@@ -2137,13 +2077,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>31</v>
@@ -2154,53 +2094,53 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2227,7 +2167,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2241,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>14</v>
@@ -2249,114 +2189,114 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -2382,14 +2322,14 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -2407,10 +2347,10 @@
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>20</v>
@@ -2418,10 +2358,10 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>20</v>
@@ -2429,10 +2369,10 @@
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>20</v>
@@ -2440,10 +2380,10 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>20</v>
@@ -2539,7 +2479,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2654,26 +2594,9 @@
         <v>45</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2690,7 +2613,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2701,7 +2624,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -2727,16 +2650,16 @@
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>32</v>
@@ -2744,16 +2667,16 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>32</v>
@@ -2761,33 +2684,33 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>32</v>
@@ -2795,84 +2718,84 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>65</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>32</v>
@@ -2880,107 +2803,107 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="4" t="s">
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="B16" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="D16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="C16" s="4" t="s">
+    </row>
+    <row r="17" ht="52" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="10" t="s">
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="11" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="19" ht="52" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>105</v>
       </c>
@@ -2991,111 +2914,77 @@
         <v>107</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="C20" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="D20" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>113</v>
+        <v>51</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E21" s="11" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="22" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="11" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3124,7 +3013,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3150,166 +3039,166 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>31</v>
@@ -3320,13 +3209,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>31</v>
@@ -3337,19 +3226,19 @@
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3365,19 +3254,19 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="5" max="5" width="55" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3403,13 +3292,13 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>31</v>
@@ -3420,121 +3309,53 @@
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>187</v>
-      </c>
       <c r="D7" s="4" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -3562,7 +3383,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3588,115 +3409,115 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>31</v>
@@ -3707,13 +3528,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>31</v>
@@ -3747,7 +3568,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3756,7 +3577,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -3782,138 +3603,138 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -3941,7 +3762,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3949,7 +3770,7 @@
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="B3" s="9"/>
       <c r="C3" s="9"/>
@@ -3971,13 +3792,13 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>16</v>
@@ -3985,13 +3806,13 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>16</v>
@@ -3999,13 +3820,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>16</v>
@@ -4013,13 +3834,13 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>16</v>
@@ -4027,13 +3848,13 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>16</v>
@@ -4041,13 +3862,13 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>16</v>
@@ -4055,13 +3876,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>16</v>
@@ -4069,13 +3890,13 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>16</v>
@@ -4083,13 +3904,13 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>16</v>
@@ -4097,13 +3918,13 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>16</v>
@@ -4111,13 +3932,13 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>16</v>
@@ -4125,13 +3946,13 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>20</v>
@@ -4139,13 +3960,13 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>16</v>
